--- a/diseases/d038/2010-2014.xlsx
+++ b/diseases/d038/2010-2014.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>26</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.4847715993948186</v>
       </c>
@@ -2706,9 +2703,6 @@
       <c r="O12" t="n">
         <v>7</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.1305154306062973</v>
       </c>
@@ -3634,9 +3628,6 @@
       <c r="O17" t="n">
         <v>6</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.111870369091112</v>
       </c>
@@ -4562,9 +4553,6 @@
       <c r="O22" t="n">
         <v>2</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.03729012303037066</v>
       </c>
@@ -5490,9 +5478,6 @@
       <c r="O27" t="n">
         <v>2</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.03729012303037066</v>
       </c>
@@ -6418,9 +6403,6 @@
       <c r="O32" t="n">
         <v>2</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.03729012303037066</v>
       </c>
@@ -7346,9 +7328,6 @@
       <c r="O37" t="n">
         <v>1</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.01864506151518533</v>
       </c>
@@ -8274,9 +8253,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -9202,9 +9178,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -10130,9 +10103,6 @@
       <c r="O52" t="n">
         <v>3</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.055935184545556</v>
       </c>
@@ -11058,9 +11028,6 @@
       <c r="O57" t="n">
         <v>16</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.2983209842429653</v>
       </c>
@@ -11986,9 +11953,6 @@
       <c r="O62" t="n">
         <v>496</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>9.247950511531924</v>
       </c>
@@ -12914,9 +12878,6 @@
       <c r="O67" t="n">
         <v>1397</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>25.92682843993058</v>
       </c>
@@ -14323,9 +14284,6 @@
       <c r="O74" t="n">
         <v>2250</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>41.75759770210724</v>
       </c>
@@ -15015,9 +14973,6 @@
       <c r="O78" t="n">
         <v>1410</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>26.1680945599872</v>
       </c>
@@ -15707,9 +15662,6 @@
       <c r="O82" t="n">
         <v>210</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>3.897375785530009</v>
       </c>
@@ -16399,9 +16351,6 @@
       <c r="O86" t="n">
         <v>19</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.3526197139289056</v>
       </c>
@@ -17091,9 +17040,6 @@
       <c r="O90" t="n">
         <v>6</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.111353593872286</v>
       </c>
@@ -17783,9 +17729,6 @@
       <c r="O94" t="n">
         <v>4</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.07423572924819065</v>
       </c>
@@ -18475,9 +18418,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -19167,9 +19107,6 @@
       <c r="O102" t="n">
         <v>3</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.05567679693614298</v>
       </c>
@@ -19859,9 +19796,6 @@
       <c r="O106" t="n">
         <v>2</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.03711786462409532</v>
       </c>
@@ -20551,9 +20485,6 @@
       <c r="O110" t="n">
         <v>7</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.1299125261843336</v>
       </c>
@@ -21243,9 +21174,6 @@
       <c r="O114" t="n">
         <v>36</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.6681215632337157</v>
       </c>
@@ -21935,9 +21863,6 @@
       <c r="O118" t="n">
         <v>547</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>10.10348872357381</v>
       </c>
@@ -23344,9 +23269,6 @@
       <c r="O125" t="n">
         <v>3821</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>70.57665523359331</v>
       </c>
@@ -24036,9 +23958,6 @@
       <c r="O129" t="n">
         <v>1505</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>27.79844703652393</v>
       </c>
@@ -24728,9 +24647,6 @@
       <c r="O133" t="n">
         <v>256</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>4.728506605548256</v>
       </c>
@@ -25420,9 +25336,6 @@
       <c r="O137" t="n">
         <v>56</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>1.034360819963681</v>
       </c>
@@ -26112,9 +26025,6 @@
       <c r="O141" t="n">
         <v>6</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.1108243735675373</v>
       </c>
@@ -26804,9 +26714,6 @@
       <c r="O145" t="n">
         <v>8</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.147765831423383</v>
       </c>
@@ -27496,9 +27403,6 @@
       <c r="O149" t="n">
         <v>4</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.0738829157116915</v>
       </c>
@@ -28188,9 +28092,6 @@
       <c r="O153" t="n">
         <v>5</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.09235364463961437</v>
       </c>
@@ -29324,9 +29225,6 @@
       <c r="O160" t="n">
         <v>7</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.1292951024954601</v>
       </c>
@@ -30608,9 +30506,6 @@
       <c r="O168" t="n">
         <v>42</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.7757706149727607</v>
       </c>
@@ -31892,9 +31787,6 @@
       <c r="O176" t="n">
         <v>172</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>3.176965375602735</v>
       </c>
@@ -33324,9 +33216,6 @@
       <c r="O185" t="n">
         <v>1244</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>22.87162857210621</v>
       </c>
@@ -35917,9 +35806,6 @@
       <c r="O200" t="n">
         <v>2964</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>54.49478061714052</v>
       </c>
@@ -37793,9 +37679,6 @@
       <c r="O212" t="n">
         <v>2182</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>40.11727776875864</v>
       </c>
@@ -39965,9 +39848,6 @@
       <c r="O226" t="n">
         <v>768</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>14.12010509917811</v>
       </c>
@@ -41841,9 +41721,6 @@
       <c r="O238" t="n">
         <v>121</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>2.224651975261135</v>
       </c>
@@ -43717,9 +43594,6 @@
       <c r="O250" t="n">
         <v>13</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0.2390121956892128</v>
       </c>
@@ -45889,9 +45763,6 @@
       <c r="O264" t="n">
         <v>4</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0.07354221405821933</v>
       </c>
@@ -47765,9 +47636,6 @@
       <c r="O276" t="n">
         <v>2</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0.03677110702910966</v>
       </c>
@@ -49789,9 +49657,6 @@
       <c r="O289" t="n">
         <v>4</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>0.07354221405821933</v>
       </c>
@@ -51813,9 +51678,6 @@
       <c r="O302" t="n">
         <v>9</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0.1654699816309935</v>
       </c>
@@ -53689,9 +53551,6 @@
       <c r="O314" t="n">
         <v>44</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>0.8089643546404126</v>
       </c>
@@ -55713,9 +55572,6 @@
       <c r="O327" t="n">
         <v>324</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>5.956919338715765</v>
       </c>
@@ -57737,9 +57593,6 @@
       <c r="O340" t="n">
         <v>782</v>
       </c>
-      <c r="Q340" t="n">
-        <v>0</v>
-      </c>
       <c r="R340" t="n">
         <v>14.31792831661444</v>
       </c>
@@ -60330,9 +60183,6 @@
       <c r="O355" t="n">
         <v>2745</v>
       </c>
-      <c r="Q355" t="n">
-        <v>0</v>
-      </c>
       <c r="R355" t="n">
         <v>50.25922407814147</v>
       </c>
@@ -62206,9 +62056,6 @@
       <c r="O367" t="n">
         <v>1258</v>
       </c>
-      <c r="Q367" t="n">
-        <v>0</v>
-      </c>
       <c r="R367" t="n">
         <v>23.0331890310754</v>
       </c>
@@ -64378,9 +64225,6 @@
       <c r="O381" t="n">
         <v>593</v>
       </c>
-      <c r="Q381" t="n">
-        <v>0</v>
-      </c>
       <c r="R381" t="n">
         <v>10.85745715057847</v>
       </c>
@@ -66254,9 +66098,6 @@
       <c r="O393" t="n">
         <v>325</v>
       </c>
-      <c r="Q393" t="n">
-        <v>0</v>
-      </c>
       <c r="R393" t="n">
         <v>5.950545655881958</v>
       </c>
@@ -68278,9 +68119,6 @@
       <c r="O406" t="n">
         <v>20</v>
       </c>
-      <c r="Q406" t="n">
-        <v>0</v>
-      </c>
       <c r="R406" t="n">
         <v>0.3661874249773513</v>
       </c>
@@ -70302,9 +70140,6 @@
       <c r="O419" t="n">
         <v>8</v>
       </c>
-      <c r="Q419" t="n">
-        <v>0</v>
-      </c>
       <c r="R419" t="n">
         <v>0.1464749699909405</v>
       </c>
@@ -72178,9 +72013,6 @@
       <c r="O431" t="n">
         <v>1</v>
       </c>
-      <c r="Q431" t="n">
-        <v>0</v>
-      </c>
       <c r="R431" t="n">
         <v>0.01830937124886756</v>
       </c>
@@ -74350,9 +74182,6 @@
       <c r="O445" t="n">
         <v>4</v>
       </c>
-      <c r="Q445" t="n">
-        <v>0</v>
-      </c>
       <c r="R445" t="n">
         <v>0.07323748499547025</v>
       </c>
@@ -76226,9 +76055,6 @@
       <c r="O457" t="n">
         <v>20</v>
       </c>
-      <c r="Q457" t="n">
-        <v>0</v>
-      </c>
       <c r="R457" t="n">
         <v>0.3661874249773513</v>
       </c>
@@ -78102,9 +77928,6 @@
       <c r="O469" t="n">
         <v>105</v>
       </c>
-      <c r="Q469" t="n">
-        <v>0</v>
-      </c>
       <c r="R469" t="n">
         <v>1.922483981131095</v>
       </c>
@@ -80273,9 +80096,6 @@
       </c>
       <c r="O483" t="n">
         <v>1285</v>
-      </c>
-      <c r="Q483" t="n">
-        <v>0</v>
       </c>
       <c r="R483" t="n">
         <v>23.52754205479482</v>
